--- a/Source_Data.xlsx
+++ b/Source_Data.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp Fig 3b" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp Fig 3c" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verified AUC (SI 4.2)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp Fig 1a-b" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp Fig 1c" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp Fig 1a" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp Fig 1b" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig 4a" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig 4b" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supp Fig 4" sheetId="12" state="visible" r:id="rId12"/>
@@ -611,19 +611,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Supp Fig 1a-b</t>
+          <t>Supp Fig 1a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Per-role statistics for the NBCTF TRON network.</t>
+          <t>Per-role mean in- and out-degree and share of addresses, NBCTF TRON network.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Supp Fig 1c</t>
+          <t>Supp Fig 1b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -33241,16 +33241,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22637</v>
+        <v>20295</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3697044661395061</v>
+        <v>0.2869179600886918</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6436559693285567</v>
+        <v>0.5806716598339194</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2309935062066528</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
   </sheetData>
